--- a/notes/envelope_viewer.xlsx
+++ b/notes/envelope_viewer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\garmin\RacePilot\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{C60037A1-0CD4-48C5-AC4E-6E9FBC836746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208159D1-E1FD-4D5F-888D-FFF33CB27A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Target Pace</t>
   </si>
@@ -79,16 +79,58 @@
     <t>Execution factor</t>
   </si>
   <si>
-    <t>Allowed delta</t>
-  </si>
-  <si>
     <t>Lower envelope factor</t>
   </si>
   <si>
-    <t>Lower envelope</t>
+    <t>Factored factored pace</t>
   </si>
   <si>
-    <t>Factored factored pace</t>
+    <t>Lower envelope - BLUE</t>
+  </si>
+  <si>
+    <t>LOWER ENVELOPE</t>
+  </si>
+  <si>
+    <t>UPPER ENVELOPE</t>
+  </si>
+  <si>
+    <t>Aggressiveness (s/km)</t>
+  </si>
+  <si>
+    <t>Aggressiveness factor</t>
+  </si>
+  <si>
+    <t>Controlled Start</t>
+  </si>
+  <si>
+    <t>Main Race</t>
+  </si>
+  <si>
+    <t>Start to Push</t>
+  </si>
+  <si>
+    <t>Empty the tank</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Ramp to main</t>
+  </si>
+  <si>
+    <t>Main race pt2</t>
+  </si>
+  <si>
+    <t>Ahead Envelope - RED</t>
+  </si>
+  <si>
+    <t>Lower envelope - GREY</t>
+  </si>
+  <si>
+    <t>Ahead Envelope - Yellow</t>
+  </si>
+  <si>
+    <t>Yellow factor</t>
   </si>
 </sst>
 </file>
@@ -97,10 +139,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[mm]:ss"/>
-    <numFmt numFmtId="166" formatCode="[h]:mm:ss.0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="[h]:mm:ss.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +158,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +207,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -155,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -168,11 +257,32 @@
     </xf>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -274,6 +384,402 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$11:$A$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21.0975</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$11:$G$32</c:f>
+              <c:numCache>
+                <c:formatCode>[mm]:ss</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>5.7870370370370454E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7870370370370454E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.7870370370370745E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.3402777777777624E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.47222222222221E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.8935185185185081E-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4801587301587213E-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.1701388888888812E-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9290123456789669E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.736111111111105E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5782828282828225E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4467592592592541E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3354700854700807E-5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2400793650793607E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1574074074074033E-5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0850694444444406E-5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.1699346405229291E-6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.7870370370371706E-6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.6549707602344896E-6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.7361111111113825E-6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-688F-403F-B601-A0DBDBFBF4A3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$L$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lower envelope - GREY</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$11:$A$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21.0975</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$L$11:$L$32</c:f>
+              <c:numCache>
+                <c:formatCode>[h]:mm:ss</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1.1630497685185187E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.215697337962963E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2567708333333333E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.484157986111111E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8631365740740742E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4463541666666671E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.855396412037037E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.1076244212962958E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.3604166666666667E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.532190393518519E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5060763888888891E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.4220920138888891E-4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.2802372685185186E-4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.080512152777778E-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.893489583333333E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.654947916666667E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1341145833333336E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6132812500000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.0924479166666668E-4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.351273148148149E-5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.6423611111111193E-6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-688F-403F-B601-A0DBDBFBF4A3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lower envelope - BLUE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
@@ -297,7 +803,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$27</c:f>
+              <c:f>Sheet1!$A$11:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
@@ -372,72 +878,72 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$6:$G$27</c:f>
+              <c:f>Sheet1!$P$11:$P$32</c:f>
               <c:numCache>
-                <c:formatCode>[mm]:ss</c:formatCode>
+                <c:formatCode>[h]:mm:ss.0</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>5.7870370370370454E-5</c:v>
+                  <c:v>8.72287326388889E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7870370370370454E-5</c:v>
+                  <c:v>9.1177300347222216E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7870370370370745E-5</c:v>
+                  <c:v>9.4257812499999995E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3402777777777624E-5</c:v>
+                  <c:v>9.6470269097222237E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.47222222222221E-5</c:v>
+                  <c:v>1.024725115740741E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.8935185185185081E-5</c:v>
+                  <c:v>1.2231770833333335E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4801587301587213E-5</c:v>
+                  <c:v>1.4276982060185185E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1701388888888812E-5</c:v>
+                  <c:v>1.5538122106481479E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.9290123456789669E-5</c:v>
+                  <c:v>1.6802083333333334E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.736111111111105E-5</c:v>
+                  <c:v>1.7660951967592595E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.5782828282828225E-5</c:v>
+                  <c:v>1.7530381944444445E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4467592592592541E-5</c:v>
+                  <c:v>1.7110460069444446E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.3354700854700807E-5</c:v>
+                  <c:v>1.6401186342592593E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.2400793650793607E-5</c:v>
+                  <c:v>1.540256076388889E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1574074074074033E-5</c:v>
+                  <c:v>1.4467447916666665E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0850694444444406E-5</c:v>
+                  <c:v>1.3274739583333335E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.1699346405229291E-6</c:v>
+                  <c:v>1.0670572916666668E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.7870370370371706E-6</c:v>
+                  <c:v>8.066406250000002E-5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.6549707602344896E-6</c:v>
+                  <c:v>5.4622395833333342E-5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.7361111111113825E-6</c:v>
+                  <c:v>3.1756365740740745E-5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2.8211805555555597E-6</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -448,20 +954,28 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-688F-403F-B601-A0DBDBFBF4A3}"/>
+              <c16:uniqueId val="{00000004-688F-403F-B601-A0DBDBFBF4A3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="3"/>
           <c:tx>
-            <c:v>Behind Envelope</c:v>
+            <c:strRef>
+              <c:f>Sheet1!$T$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ahead Envelope - RED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="DC241F"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -472,11 +986,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="DC241F"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="DC241F"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -484,7 +998,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$27</c:f>
+              <c:f>Sheet1!$A$11:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
@@ -559,75 +1073,75 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$L$6:$L$27</c:f>
+              <c:f>Sheet1!$T$11:$T$32</c:f>
               <c:numCache>
-                <c:formatCode>[h]:mm:ss</c:formatCode>
+                <c:formatCode>[mm]:ss</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>1.1630497685185187E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.215697337962963E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2567708333333333E-4</c:v>
+                  <c:v>-2.314814814814815E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.484157986111111E-4</c:v>
+                  <c:v>-2.8935185185185186E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.8631365740740742E-4</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.4463541666666671E-4</c:v>
+                  <c:v>-4.0509259259259258E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.855396412037037E-4</c:v>
+                  <c:v>-4.6296296296296301E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.1076244212962958E-4</c:v>
+                  <c:v>-5.2083333333333337E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3604166666666667E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.532190393518519E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.5060763888888891E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.4220920138888891E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.2802372685185186E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.080512152777778E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.893489583333333E-4</c:v>
+                  <c:v>-5.7870370370370373E-5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.654947916666667E-4</c:v>
+                  <c:v>-7.5231481481481487E-5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.1341145833333336E-4</c:v>
+                  <c:v>-1.1574074074074075E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.6132812500000004E-4</c:v>
+                  <c:v>-1.4467592592592592E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.0924479166666668E-4</c:v>
+                  <c:v>-1.7361111111111112E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.351273148148149E-5</c:v>
+                  <c:v>-1.7361111111111112E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.6423611111111193E-6</c:v>
+                  <c:v>-1.7361111111111112E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>-1.7361111111111112E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -635,20 +1149,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-688F-403F-B601-A0DBDBFBF4A3}"/>
+              <c16:uniqueId val="{00000000-BD20-4F9D-A325-72F53C5E0E4F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="3"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$5</c:f>
+              <c:f>Sheet1!$V$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Factored Pace delta for rest of race</c:v>
+                  <c:v>Ahead Envelope - Yellow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -656,7 +1170,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -667,11 +1181,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:srgbClr val="FFC000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -679,7 +1193,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$27</c:f>
+              <c:f>Sheet1!$A$11:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
@@ -754,75 +1268,75 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$M$6:$M$27</c:f>
+              <c:f>Sheet1!$V$11:$V$32</c:f>
               <c:numCache>
-                <c:formatCode>[h]:mm:ss.0</c:formatCode>
+                <c:formatCode>[mm]:ss</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>5.7870370370370376E-6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3657407407407403E-6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.9444444444444439E-6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.6805555555555555E-6</c:v>
+                  <c:v>-7.2337962962962966E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.1574074074074075E-5</c:v>
+                  <c:v>-1.7361111111111111E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.6203703703703707E-5</c:v>
+                  <c:v>-2.0254629629629629E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.0254629629629629E-5</c:v>
+                  <c:v>-2.314814814814815E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.3726851851851847E-5</c:v>
+                  <c:v>-2.6041666666666668E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.7777777777777779E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.1828703703703708E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.4722222222222222E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.7615740740740744E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.0509259259259258E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.3402777777777779E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.7453703703703694E-5</c:v>
+                  <c:v>-3.4722222222222222E-5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.2083333333333337E-5</c:v>
+                  <c:v>-4.5138888888888894E-5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.2083333333333337E-5</c:v>
+                  <c:v>-6.9444444444444444E-5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.2083333333333343E-5</c:v>
+                  <c:v>-1.0127314814814813E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.2083333333333337E-5</c:v>
+                  <c:v>-1.3888888888888889E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.7870370370370373E-5</c:v>
+                  <c:v>-1.5625E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.7870370370370373E-5</c:v>
+                  <c:v>-1.5625E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>-1.5625E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -830,397 +1344,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-688F-403F-B601-A0DBDBFBF4A3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$O$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Factored factored pace</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$6:$A$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21.0975</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$O$6:$O$27</c:f>
-              <c:numCache>
-                <c:formatCode>[h]:mm:ss.0</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>5.7870370370370376E-6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.3657407407407403E-6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.9444444444444439E-6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.246527777777777E-6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.0416666666666668E-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.4583333333333337E-5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.8229166666666668E-5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.1354166666666663E-5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.5000000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.8645833333333336E-5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.1250000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.3854166666666672E-5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.6458333333333336E-5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3.9062500000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.2708333333333326E-5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.6875000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4.6875000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>4.6875000000000008E-5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>4.6875000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.2083333333333337E-5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.2083333333333337E-5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-688F-403F-B601-A0DBDBFBF4A3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$P$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lower envelope</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$6:$A$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21.0975</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$6:$P$27</c:f>
-              <c:numCache>
-                <c:formatCode>[h]:mm:ss.0</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>1.1630497685185187E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2156973379629628E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.2567708333333333E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4099500868055556E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.676822916666667E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.2017187500000004E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.5698567708333335E-4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.7968619791666664E-4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.0243750000000003E-4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.1789713541666669E-4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.1554687500000002E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.0798828125000005E-4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.9522135416666672E-4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.7724609374999999E-4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.6041406249999996E-4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.3894531250000001E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.9207031250000002E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.4519531250000003E-4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9.8320312500000005E-5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.7161458333333347E-5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.0781250000000074E-6</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-688F-403F-B601-A0DBDBFBF4A3}"/>
+              <c16:uniqueId val="{00000000-27A2-4604-BD64-68DB44048929}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2112,16 +2236,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>433387</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>428904</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>173128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>204787</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>11204</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2585,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
@@ -2600,25 +2724,40 @@
     <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.375" customWidth="1"/>
     <col min="16" max="16" width="12.875" customWidth="1"/>
+    <col min="17" max="17" width="2.125" customWidth="1"/>
+    <col min="18" max="18" width="18.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1">
         <v>21.0975</v>
       </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
         <v>7.2916666666666671E-2</v>
       </c>
+      <c r="D2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <f>E3-1</f>
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2626,696 +2765,549 @@
         <f>B2/B1</f>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B4" s="1"/>
+      <c r="D4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <f>(E5+E3)/2</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B5" s="1"/>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B6" s="1"/>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <f>B1</f>
+        <v>21.0975</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="H9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="R9" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="9" t="s">
+      <c r="P10" s="12" t="s">
         <v>16</v>
       </c>
+      <c r="R10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>1</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B11" s="1">
         <f>$B$3</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="C6" s="1">
-        <f>B6*$A6</f>
+      <c r="C11" s="1">
+        <f>B11*$A11</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="D6" s="2">
-        <f>B6+TIME(0,0,5)</f>
+      <c r="D11" s="2">
+        <f>B11+TIME(0,0,5)</f>
         <v>3.5140460625929879E-3</v>
       </c>
-      <c r="E6" s="1">
-        <f>D6*$A6</f>
+      <c r="E11" s="1">
+        <f>D11*$A11</f>
         <v>3.5140460625929879E-3</v>
       </c>
-      <c r="F6" s="1">
-        <f>E6-C6</f>
+      <c r="F11" s="1">
+        <f>E11-C11</f>
         <v>5.7870370370370454E-5</v>
       </c>
-      <c r="G6" s="1">
-        <f>F6/A6</f>
+      <c r="G11" s="1">
+        <f>F11/A11</f>
         <v>5.7870370370370454E-5</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H11" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I6">
-        <f>$A$27-A6</f>
+      <c r="I11">
+        <f>$A$32-A11</f>
         <v>20.0975</v>
       </c>
-      <c r="J6" s="6">
-        <f>H6*I6</f>
+      <c r="J11" s="6">
+        <f>H11*I11</f>
         <v>1.1630497685185186E-3</v>
       </c>
-      <c r="K6">
+      <c r="K11">
         <v>0.1</v>
       </c>
-      <c r="L6" s="6">
-        <f>K6*J6</f>
+      <c r="L11" s="6">
+        <f>K11*J11</f>
         <v>1.1630497685185187E-4</v>
       </c>
-      <c r="M6" s="8">
-        <f>L6/I6</f>
+      <c r="M11" s="8">
+        <f>L11/I11</f>
         <v>5.7870370370370376E-6</v>
       </c>
-      <c r="N6" s="10">
-        <v>1</v>
-      </c>
-      <c r="O6" s="8">
-        <f>N6*M6</f>
-        <v>5.7870370370370376E-6</v>
-      </c>
-      <c r="P6" s="8">
-        <f>M6*N6*I6</f>
-        <v>1.1630497685185187E-4</v>
+      <c r="N11" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="O11" s="8">
+        <f>N11*M11</f>
+        <v>4.3402777777777786E-6</v>
+      </c>
+      <c r="P11" s="8">
+        <f>M11*N11*I11</f>
+        <v>8.72287326388889E-5</v>
+      </c>
+      <c r="R11" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S11" s="10">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <f>R11*S11*-1</f>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.5</v>
+      </c>
+      <c r="V11" s="1">
+        <f>T11*U11</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>2</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B12" s="1">
         <f>$B$3</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="C7" s="1">
-        <f>C6+(B7*($A7-$A6))</f>
+      <c r="C12" s="1">
+        <f>C11+(B12*($A12-$A11))</f>
         <v>6.9123513844452349E-3</v>
       </c>
-      <c r="D7" s="2">
-        <f t="shared" ref="D7:D8" si="0">B7+TIME(0,0,5)</f>
+      <c r="D12" s="2">
+        <f t="shared" ref="D12:D13" si="0">B12+TIME(0,0,5)</f>
         <v>3.5140460625929879E-3</v>
       </c>
-      <c r="E7" s="1">
-        <f>E6+(D7*($A7-$A6))</f>
+      <c r="E12" s="1">
+        <f>E11+(D12*($A12-$A11))</f>
         <v>7.0280921251859758E-3</v>
       </c>
-      <c r="F7" s="1">
-        <f t="shared" ref="F7:F27" si="1">E7-C7</f>
+      <c r="F12" s="1">
+        <f t="shared" ref="F12:F31" si="1">E12-C12</f>
         <v>1.1574074074074091E-4</v>
       </c>
-      <c r="G7" s="1">
-        <f t="shared" ref="G7:G27" si="2">F7/A7</f>
+      <c r="G12" s="1">
+        <f t="shared" ref="G12:G32" si="2">F12/A12</f>
         <v>5.7870370370370454E-5</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H12" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I7">
-        <f t="shared" ref="I7:I27" si="3">$A$27-A7</f>
+      <c r="I12">
+        <f t="shared" ref="I12:I32" si="3">$A$32-A12</f>
         <v>19.0975</v>
       </c>
-      <c r="J7" s="6">
-        <f t="shared" ref="J7:J27" si="4">H7*I7</f>
+      <c r="J12" s="6">
+        <f t="shared" ref="J12:J32" si="4">H12*I12</f>
         <v>1.1051793981481481E-3</v>
       </c>
-      <c r="K7">
+      <c r="K12">
         <v>0.11</v>
       </c>
-      <c r="L7" s="6">
-        <f t="shared" ref="L7:L27" si="5">K7*J7</f>
+      <c r="L12" s="6">
+        <f t="shared" ref="L12:L32" si="5">K12*J12</f>
         <v>1.215697337962963E-4</v>
       </c>
-      <c r="M7" s="8">
-        <f t="shared" ref="M7:M26" si="6">L7/I7</f>
+      <c r="M12" s="8">
+        <f t="shared" ref="M12:M31" si="6">L12/I12</f>
         <v>6.3657407407407403E-6</v>
       </c>
-      <c r="N7" s="10">
-        <v>1</v>
-      </c>
-      <c r="O7" s="8">
-        <f t="shared" ref="O7:O27" si="7">N7*M7</f>
-        <v>6.3657407407407403E-6</v>
-      </c>
-      <c r="P7" s="8">
-        <f t="shared" ref="P7:P27" si="8">M7*N7*I7</f>
-        <v>1.2156973379629628E-4</v>
+      <c r="N12" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="O12" s="8">
+        <f t="shared" ref="O12:O32" si="7">N12*M12</f>
+        <v>4.7743055555555555E-6</v>
+      </c>
+      <c r="P12" s="8">
+        <f t="shared" ref="P12:P32" si="8">M12*N12*I12</f>
+        <v>9.1177300347222216E-5</v>
+      </c>
+      <c r="R12" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S12" s="17">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" ref="T12:T32" si="9">R12*S12*-1</f>
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0.5</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ref="V12:V32" si="10">T12*U12</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>3</v>
       </c>
-      <c r="B8" s="1">
-        <f t="shared" ref="B8:B27" si="9">$B$3</f>
+      <c r="B13" s="1">
+        <f t="shared" ref="B13:B32" si="11">$B$3</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="C8" s="1">
-        <f t="shared" ref="C8:E27" si="10">C7+(B8*($A8-$A7))</f>
+      <c r="C13" s="1">
+        <f t="shared" ref="C13:E32" si="12">C12+(B13*($A13-$A12))</f>
         <v>1.0368527076667852E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D13" s="2">
         <f t="shared" si="0"/>
         <v>3.5140460625929879E-3</v>
       </c>
-      <c r="E8" s="1">
-        <f t="shared" si="10"/>
+      <c r="E13" s="1">
+        <f t="shared" si="12"/>
         <v>1.0542138187778964E-2</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F13" s="1">
         <f t="shared" si="1"/>
         <v>1.7361111111111223E-4</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G13" s="1">
         <f t="shared" si="2"/>
         <v>5.7870370370370745E-5</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H13" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I8">
+      <c r="I13">
         <f t="shared" si="3"/>
         <v>18.0975</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J13" s="6">
         <f t="shared" si="4"/>
         <v>1.0473090277777779E-3</v>
       </c>
-      <c r="K8">
+      <c r="K13">
         <v>0.12</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L13" s="6">
         <f t="shared" si="5"/>
         <v>1.2567708333333333E-4</v>
       </c>
-      <c r="M8" s="8">
-        <f>L8/I8</f>
+      <c r="M13" s="8">
+        <f>L13/I13</f>
         <v>6.9444444444444439E-6</v>
       </c>
-      <c r="N8" s="10">
-        <v>1</v>
-      </c>
-      <c r="O8" s="8">
+      <c r="N13" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="O13" s="8">
         <f t="shared" si="7"/>
-        <v>6.9444444444444439E-6</v>
-      </c>
-      <c r="P8" s="8">
+        <v>5.2083333333333332E-6</v>
+      </c>
+      <c r="P13" s="8">
         <f t="shared" si="8"/>
-        <v>1.2567708333333333E-4</v>
+        <v>9.4257812499999995E-5</v>
+      </c>
+      <c r="R13" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" si="9"/>
+        <v>-2.314814814814815E-5</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>4</v>
       </c>
-      <c r="B9" s="1">
-        <f t="shared" si="9"/>
+      <c r="B14" s="1">
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="C9" s="1">
-        <f t="shared" si="10"/>
+      <c r="C14" s="1">
+        <f t="shared" si="12"/>
         <v>1.382470276889047E-2</v>
       </c>
-      <c r="D9" s="1">
-        <f>B9</f>
+      <c r="D14" s="1">
+        <f>B14</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="E9" s="1">
-        <f t="shared" si="10"/>
+      <c r="E14" s="1">
+        <f t="shared" si="12"/>
         <v>1.399831388000158E-2</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F14" s="1">
         <f t="shared" si="1"/>
         <v>1.7361111111111049E-4</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G14" s="1">
         <f t="shared" si="2"/>
         <v>4.3402777777777624E-5</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H14" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I9">
+      <c r="I14">
         <f t="shared" si="3"/>
         <v>17.0975</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J14" s="6">
         <f t="shared" si="4"/>
         <v>9.8943865740740741E-4</v>
       </c>
-      <c r="K9">
+      <c r="K14">
         <v>0.15</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L14" s="6">
         <f t="shared" si="5"/>
         <v>1.484157986111111E-4</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M14" s="8">
         <f t="shared" si="6"/>
         <v>8.6805555555555555E-6</v>
       </c>
-      <c r="N9" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="O9" s="8">
+      <c r="N14" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="O14" s="8">
         <f t="shared" si="7"/>
-        <v>8.246527777777777E-6</v>
-      </c>
-      <c r="P9" s="8">
+        <v>5.6423611111111117E-6</v>
+      </c>
+      <c r="P14" s="8">
         <f t="shared" si="8"/>
-        <v>1.4099500868055556E-4</v>
+        <v>9.6470269097222237E-5</v>
+      </c>
+      <c r="R14" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S14" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" si="9"/>
+        <v>-2.8935185185185186E-5</v>
+      </c>
+      <c r="U14">
+        <v>0.25</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" si="10"/>
+        <v>-7.2337962962962966E-6</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>5</v>
       </c>
-      <c r="B10" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="10"/>
-        <v>1.7280878461113088E-2</v>
-      </c>
-      <c r="D10" s="1">
-        <f t="shared" ref="D10:D27" si="11">B10</f>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" si="10"/>
-        <v>1.7454489572224199E-2</v>
-      </c>
-      <c r="F10" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7361111111111049E-4</v>
-      </c>
-      <c r="G10" s="1">
-        <f>F10/A10</f>
-        <v>3.47222222222221E-5</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="3"/>
-        <v>16.0975</v>
-      </c>
-      <c r="J10" s="6">
-        <f t="shared" si="4"/>
-        <v>9.3156828703703707E-4</v>
-      </c>
-      <c r="K10">
-        <v>0.2</v>
-      </c>
-      <c r="L10" s="6">
-        <f t="shared" si="5"/>
-        <v>1.8631365740740742E-4</v>
-      </c>
-      <c r="M10" s="8">
-        <f t="shared" si="6"/>
-        <v>1.1574074074074075E-5</v>
-      </c>
-      <c r="N10" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="O10" s="8">
-        <f t="shared" si="7"/>
-        <v>1.0416666666666668E-5</v>
-      </c>
-      <c r="P10" s="8">
-        <f t="shared" si="8"/>
-        <v>1.676822916666667E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="10"/>
-        <v>2.0737054153335707E-2</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B15" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="E11" s="1">
-        <f t="shared" si="10"/>
-        <v>2.0910665264446817E-2</v>
-      </c>
-      <c r="F11" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7361111111111049E-4</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="2"/>
-        <v>2.8935185185185081E-5</v>
-      </c>
-      <c r="H11" s="1">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="3"/>
-        <v>15.0975</v>
-      </c>
-      <c r="J11" s="6">
-        <f t="shared" si="4"/>
-        <v>8.7369791666666672E-4</v>
-      </c>
-      <c r="K11" s="7">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L11" s="6">
-        <f t="shared" si="5"/>
-        <v>2.4463541666666671E-4</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="6"/>
-        <v>1.6203703703703707E-5</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="O11" s="8">
-        <f t="shared" si="7"/>
-        <v>1.4583333333333337E-5</v>
-      </c>
-      <c r="P11" s="8">
-        <f t="shared" si="8"/>
-        <v>2.2017187500000004E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="9"/>
+      <c r="C15" s="1">
+        <f t="shared" si="12"/>
+        <v>1.7280878461113088E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" ref="D15:D26" si="13">B15</f>
         <v>3.4561756922226175E-3</v>
       </c>
-      <c r="C12" s="1">
-        <f t="shared" si="10"/>
-        <v>2.4193229845558325E-2</v>
-      </c>
-      <c r="D12" s="1">
-        <f t="shared" si="11"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="E12" s="1">
-        <f t="shared" si="10"/>
-        <v>2.4366840956669435E-2</v>
-      </c>
-      <c r="F12" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7361111111111049E-4</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="2"/>
-        <v>2.4801587301587213E-5</v>
-      </c>
-      <c r="H12" s="1">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="3"/>
-        <v>14.0975</v>
-      </c>
-      <c r="J12" s="6">
-        <f t="shared" si="4"/>
-        <v>8.1582754629629637E-4</v>
-      </c>
-      <c r="K12">
-        <v>0.35</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="5"/>
-        <v>2.855396412037037E-4</v>
-      </c>
-      <c r="M12" s="8">
-        <f t="shared" si="6"/>
-        <v>2.0254629629629629E-5</v>
-      </c>
-      <c r="N12" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="O12" s="8">
-        <f t="shared" si="7"/>
-        <v>1.8229166666666668E-5</v>
-      </c>
-      <c r="P12" s="8">
-        <f t="shared" si="8"/>
-        <v>2.5698567708333335E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="10"/>
-        <v>2.7649405537780943E-2</v>
-      </c>
-      <c r="D13" s="1">
-        <f t="shared" si="11"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="10"/>
-        <v>2.7823016648892054E-2</v>
-      </c>
-      <c r="F13" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7361111111111049E-4</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="2"/>
-        <v>2.1701388888888812E-5</v>
-      </c>
-      <c r="H13" s="1">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="3"/>
-        <v>13.0975</v>
-      </c>
-      <c r="J13" s="6">
-        <f t="shared" si="4"/>
-        <v>7.5795717592592592E-4</v>
-      </c>
-      <c r="K13">
-        <v>0.41</v>
-      </c>
-      <c r="L13" s="6">
-        <f t="shared" si="5"/>
-        <v>3.1076244212962958E-4</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" si="6"/>
-        <v>2.3726851851851847E-5</v>
-      </c>
-      <c r="N13" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" si="7"/>
-        <v>2.1354166666666663E-5</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="8"/>
-        <v>2.7968619791666664E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="10"/>
-        <v>3.1105581230003562E-2</v>
-      </c>
-      <c r="D14" s="1">
-        <f t="shared" si="11"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="10"/>
-        <v>3.1279192341114669E-2</v>
-      </c>
-      <c r="F14" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7361111111110702E-4</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="2"/>
-        <v>1.9290123456789669E-5</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="3"/>
-        <v>12.0975</v>
-      </c>
-      <c r="J14" s="6">
-        <f t="shared" si="4"/>
-        <v>7.0008680555555558E-4</v>
-      </c>
-      <c r="K14">
-        <v>0.48</v>
-      </c>
-      <c r="L14" s="6">
-        <f t="shared" si="5"/>
-        <v>3.3604166666666667E-4</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="6"/>
-        <v>2.7777777777777779E-5</v>
-      </c>
-      <c r="N14" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="7"/>
-        <v>2.5000000000000001E-5</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="8"/>
-        <v>3.0243750000000003E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="10"/>
-        <v>3.4561756922226176E-2</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" si="11"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
       <c r="E15" s="1">
-        <f t="shared" si="10"/>
-        <v>3.4735368033337287E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.7454489572224199E-2</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="1"/>
         <v>1.7361111111111049E-4</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="2"/>
-        <v>1.736111111111105E-5</v>
+        <f>F15/A15</f>
+        <v>3.47222222222221E-5</v>
       </c>
       <c r="H15" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I15">
         <f t="shared" si="3"/>
-        <v>11.0975</v>
+        <v>16.0975</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="4"/>
-        <v>6.4221643518518523E-4</v>
+        <v>9.3156828703703707E-4</v>
       </c>
       <c r="K15">
-        <v>0.55000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="5"/>
-        <v>3.532190393518519E-4</v>
+        <v>1.8631365740740742E-4</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="6"/>
-        <v>3.1828703703703708E-5</v>
+        <v>1.1574074074074075E-5</v>
       </c>
       <c r="N15" s="10">
-        <v>0.9</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="7"/>
-        <v>2.8645833333333336E-5</v>
+        <v>6.365740740740742E-6</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" si="8"/>
-        <v>3.1789713541666669E-4</v>
+        <v>1.024725115740741E-4</v>
+      </c>
+      <c r="R15" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S15" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" si="9"/>
+        <v>-3.4722222222222222E-5</v>
+      </c>
+      <c r="U15">
+        <v>0.5</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.7361111111111111E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="10"/>
-        <v>3.8017932614448795E-2</v>
-      </c>
-      <c r="D16" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C16" s="1">
+        <f t="shared" si="12"/>
+        <v>2.0737054153335707E-2</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E16" s="1">
-        <f t="shared" si="10"/>
-        <v>3.8191543725559905E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.0910665264446817E-2</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="1"/>
@@ -3323,61 +3315,78 @@
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>1.5782828282828225E-5</v>
+        <v>2.8935185185185081E-5</v>
       </c>
       <c r="H16" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>10.0975</v>
+        <v>15.0975</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="4"/>
-        <v>5.8434606481481488E-4</v>
+        <v>8.7369791666666672E-4</v>
       </c>
       <c r="K16" s="7">
-        <v>0.6</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="5"/>
-        <v>3.5060763888888891E-4</v>
+        <v>2.4463541666666671E-4</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="6"/>
-        <v>3.4722222222222222E-5</v>
+        <v>1.6203703703703707E-5</v>
       </c>
       <c r="N16" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="7"/>
-        <v>3.1250000000000001E-5</v>
+        <v>8.1018518518518537E-6</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="8"/>
-        <v>3.1554687500000002E-4</v>
+        <v>1.2231770833333335E-4</v>
+      </c>
+      <c r="R16" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S16" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="T16" s="1">
+        <f t="shared" si="9"/>
+        <v>-4.0509259259259258E-5</v>
+      </c>
+      <c r="U16">
+        <v>0.5</v>
+      </c>
+      <c r="V16" s="1">
+        <f t="shared" si="10"/>
+        <v>-2.0254629629629629E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="10"/>
-        <v>4.1474108306671413E-2</v>
-      </c>
-      <c r="D17" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C17" s="1">
+        <f t="shared" si="12"/>
+        <v>2.4193229845558325E-2</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E17" s="1">
-        <f t="shared" si="10"/>
-        <v>4.1647719417782524E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.4366840956669435E-2</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="1"/>
@@ -3385,61 +3394,78 @@
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4467592592592541E-5</v>
+        <v>2.4801587301587213E-5</v>
       </c>
       <c r="H17" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>9.0975000000000001</v>
+        <v>14.0975</v>
       </c>
       <c r="J17" s="6">
         <f t="shared" si="4"/>
-        <v>5.2647569444444443E-4</v>
+        <v>8.1582754629629637E-4</v>
       </c>
       <c r="K17">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="L17" s="6">
         <f t="shared" si="5"/>
-        <v>3.4220920138888891E-4</v>
+        <v>2.855396412037037E-4</v>
       </c>
       <c r="M17" s="8">
         <f t="shared" si="6"/>
-        <v>3.7615740740740744E-5</v>
+        <v>2.0254629629629629E-5</v>
       </c>
       <c r="N17" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="7"/>
-        <v>3.3854166666666672E-5</v>
+        <v>1.0127314814814815E-5</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="8"/>
-        <v>3.0798828125000005E-4</v>
+        <v>1.4276982060185185E-4</v>
+      </c>
+      <c r="R17" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S17" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="T17" s="1">
+        <f t="shared" si="9"/>
+        <v>-4.6296296296296301E-5</v>
+      </c>
+      <c r="U17">
+        <v>0.5</v>
+      </c>
+      <c r="V17" s="1">
+        <f t="shared" si="10"/>
+        <v>-2.314814814814815E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" si="10"/>
-        <v>4.4930283998894031E-2</v>
-      </c>
-      <c r="D18" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C18" s="1">
+        <f t="shared" si="12"/>
+        <v>2.7649405537780943E-2</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E18" s="1">
-        <f t="shared" si="10"/>
-        <v>4.5103895110005142E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.7823016648892054E-2</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="1"/>
@@ -3447,123 +3473,157 @@
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>1.3354700854700807E-5</v>
+        <v>2.1701388888888812E-5</v>
       </c>
       <c r="H18" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I18">
         <f t="shared" si="3"/>
-        <v>8.0975000000000001</v>
+        <v>13.0975</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="4"/>
-        <v>4.6860532407407408E-4</v>
+        <v>7.5795717592592592E-4</v>
       </c>
       <c r="K18">
-        <v>0.7</v>
+        <v>0.41</v>
       </c>
       <c r="L18" s="6">
         <f t="shared" si="5"/>
-        <v>3.2802372685185186E-4</v>
+        <v>3.1076244212962958E-4</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="6"/>
-        <v>4.0509259259259258E-5</v>
+        <v>2.3726851851851847E-5</v>
       </c>
       <c r="N18" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="7"/>
-        <v>3.6458333333333336E-5</v>
+        <v>1.1863425925925924E-5</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="8"/>
-        <v>2.9522135416666672E-4</v>
+        <v>1.5538122106481479E-4</v>
+      </c>
+      <c r="R18" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S18" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="T18" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.2083333333333337E-5</v>
+      </c>
+      <c r="U18">
+        <v>0.5</v>
+      </c>
+      <c r="V18" s="1">
+        <f t="shared" si="10"/>
+        <v>-2.6041666666666668E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" si="10"/>
-        <v>4.838645969111665E-2</v>
-      </c>
-      <c r="D19" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C19" s="1">
+        <f t="shared" si="12"/>
+        <v>3.1105581230003562E-2</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E19" s="1">
-        <f t="shared" si="10"/>
-        <v>4.856007080222776E-2</v>
+        <f t="shared" si="12"/>
+        <v>3.1279192341114669E-2</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="1"/>
-        <v>1.7361111111111049E-4</v>
+        <v>1.7361111111110702E-4</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>1.2400793650793607E-5</v>
+        <v>1.9290123456789669E-5</v>
       </c>
       <c r="H19" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I19">
         <f t="shared" si="3"/>
-        <v>7.0975000000000001</v>
+        <v>12.0975</v>
       </c>
       <c r="J19" s="6">
         <f t="shared" si="4"/>
-        <v>4.1073495370370374E-4</v>
+        <v>7.0008680555555558E-4</v>
       </c>
       <c r="K19">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="L19" s="6">
         <f t="shared" si="5"/>
-        <v>3.080512152777778E-4</v>
+        <v>3.3604166666666667E-4</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="6"/>
-        <v>4.3402777777777779E-5</v>
+        <v>2.7777777777777779E-5</v>
       </c>
       <c r="N19" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="7"/>
-        <v>3.9062500000000001E-5</v>
+        <v>1.388888888888889E-5</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="8"/>
-        <v>2.7724609374999999E-4</v>
+        <v>1.6802083333333334E-4</v>
+      </c>
+      <c r="R19" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S19" s="17">
+        <v>1</v>
+      </c>
+      <c r="T19" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U19">
+        <v>0.6</v>
+      </c>
+      <c r="V19" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" si="10"/>
-        <v>5.1842635383339268E-2</v>
-      </c>
-      <c r="D20" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C20" s="1">
+        <f t="shared" si="12"/>
+        <v>3.4561756922226176E-2</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E20" s="1">
-        <f t="shared" si="10"/>
-        <v>5.2016246494450379E-2</v>
+        <f t="shared" si="12"/>
+        <v>3.4735368033337287E-2</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="1"/>
@@ -3571,61 +3631,78 @@
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>1.1574074074074033E-5</v>
+        <v>1.736111111111105E-5</v>
       </c>
       <c r="H20" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>6.0975000000000001</v>
+        <v>11.0975</v>
       </c>
       <c r="J20" s="6">
         <f t="shared" si="4"/>
-        <v>3.5286458333333334E-4</v>
+        <v>6.4221643518518523E-4</v>
       </c>
       <c r="K20">
-        <v>0.82</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="5"/>
-        <v>2.893489583333333E-4</v>
+        <v>3.532190393518519E-4</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="6"/>
-        <v>4.7453703703703694E-5</v>
+        <v>3.1828703703703708E-5</v>
       </c>
       <c r="N20" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="7"/>
-        <v>4.2708333333333326E-5</v>
+        <v>1.5914351851851854E-5</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="8"/>
-        <v>2.6041406249999996E-4</v>
+        <v>1.7660951967592595E-4</v>
+      </c>
+      <c r="R20" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S20" s="10">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U20">
+        <v>0.6</v>
+      </c>
+      <c r="V20" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="9"/>
-        <v>3.4561756922226175E-3</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" si="10"/>
-        <v>5.5298811075561886E-2</v>
-      </c>
-      <c r="D21" s="1">
         <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
+      <c r="C21" s="1">
+        <f t="shared" si="12"/>
+        <v>3.8017932614448795E-2</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
       <c r="E21" s="1">
-        <f t="shared" si="10"/>
-        <v>5.5472422186672997E-2</v>
+        <f t="shared" si="12"/>
+        <v>3.8191543725559905E-2</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="1"/>
@@ -3633,410 +3710,927 @@
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>1.0850694444444406E-5</v>
+        <v>1.5782828282828225E-5</v>
       </c>
       <c r="H21" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>5.0975000000000001</v>
+        <v>10.0975</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="4"/>
-        <v>2.9499421296296299E-4</v>
+        <v>5.8434606481481488E-4</v>
       </c>
       <c r="K21" s="7">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="5"/>
-        <v>2.654947916666667E-4</v>
+        <v>3.5060763888888891E-4</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="6"/>
-        <v>5.2083333333333337E-5</v>
+        <v>3.4722222222222222E-5</v>
       </c>
       <c r="N21" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="7"/>
-        <v>4.6875000000000001E-5</v>
+        <v>1.7361111111111111E-5</v>
       </c>
       <c r="P21" s="8">
         <f t="shared" si="8"/>
-        <v>2.3894531250000001E-4</v>
+        <v>1.7530381944444445E-4</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S21" s="10">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U21">
+        <v>0.6</v>
+      </c>
+      <c r="V21" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="10"/>
-        <v>5.8754986767784505E-2</v>
-      </c>
-      <c r="D22" s="3">
-        <f t="shared" ref="D22:D27" si="12">B22-TIME(0,0,3)</f>
-        <v>3.4214534700003955E-3</v>
+        <f t="shared" si="12"/>
+        <v>4.1474108306671413E-2</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="10"/>
-        <v>5.8893875656673395E-2</v>
+        <f t="shared" si="12"/>
+        <v>4.1647719417782524E-2</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" si="1"/>
-        <v>1.3888888888888978E-4</v>
+        <v>1.7361111111111049E-4</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="2"/>
-        <v>8.1699346405229291E-6</v>
+        <v>1.4467592592592541E-5</v>
       </c>
       <c r="H22" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I22">
         <f t="shared" si="3"/>
-        <v>4.0975000000000001</v>
+        <v>9.0975000000000001</v>
       </c>
       <c r="J22" s="6">
         <f t="shared" si="4"/>
-        <v>2.3712384259259262E-4</v>
+        <v>5.2647569444444443E-4</v>
       </c>
       <c r="K22">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="L22" s="6">
         <f t="shared" si="5"/>
-        <v>2.1341145833333336E-4</v>
+        <v>3.4220920138888891E-4</v>
       </c>
       <c r="M22" s="8">
         <f t="shared" si="6"/>
-        <v>5.2083333333333337E-5</v>
+        <v>3.7615740740740744E-5</v>
       </c>
       <c r="N22" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="7"/>
-        <v>4.6875000000000001E-5</v>
+        <v>1.8807870370370372E-5</v>
       </c>
       <c r="P22" s="8">
         <f t="shared" si="8"/>
-        <v>1.9207031250000002E-4</v>
+        <v>1.7110460069444446E-4</v>
+      </c>
+      <c r="R22" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S22" s="10">
+        <v>1</v>
+      </c>
+      <c r="T22" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U22">
+        <v>0.6</v>
+      </c>
+      <c r="V22" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="10"/>
-        <v>6.2211162460007123E-2</v>
-      </c>
-      <c r="D23" s="3">
         <f t="shared" si="12"/>
-        <v>3.4214534700003955E-3</v>
+        <v>4.4930283998894031E-2</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="10"/>
-        <v>6.2315329126673792E-2</v>
+        <f t="shared" si="12"/>
+        <v>4.5103895110005142E-2</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" si="1"/>
-        <v>1.0416666666666907E-4</v>
+        <v>1.7361111111111049E-4</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="2"/>
-        <v>5.7870370370371706E-6</v>
+        <v>1.3354700854700807E-5</v>
       </c>
       <c r="H23" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I23">
         <f t="shared" si="3"/>
-        <v>3.0975000000000001</v>
+        <v>8.0975000000000001</v>
       </c>
       <c r="J23" s="6">
         <f t="shared" si="4"/>
-        <v>1.7925347222222225E-4</v>
+        <v>4.6860532407407408E-4</v>
       </c>
       <c r="K23">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="5"/>
-        <v>1.6132812500000004E-4</v>
+        <v>3.2802372685185186E-4</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="6"/>
-        <v>5.2083333333333343E-5</v>
+        <v>4.0509259259259258E-5</v>
       </c>
       <c r="N23" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="7"/>
-        <v>4.6875000000000008E-5</v>
+        <v>2.0254629629629629E-5</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="8"/>
-        <v>1.4519531250000003E-4</v>
+        <v>1.6401186342592593E-4</v>
+      </c>
+      <c r="R23" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S23" s="10">
+        <v>1</v>
+      </c>
+      <c r="T23" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U23">
+        <v>0.6</v>
+      </c>
+      <c r="V23" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="10"/>
-        <v>6.5667338152229734E-2</v>
-      </c>
-      <c r="D24" s="3">
         <f t="shared" si="12"/>
-        <v>3.4214534700003955E-3</v>
+        <v>4.838645969111665E-2</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="10"/>
-        <v>6.573678259667419E-2</v>
+        <f t="shared" si="12"/>
+        <v>4.856007080222776E-2</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" si="1"/>
-        <v>6.94444444444553E-5</v>
+        <v>1.7361111111111049E-4</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="2"/>
-        <v>3.6549707602344896E-6</v>
+        <v>1.2400793650793607E-5</v>
       </c>
       <c r="H24" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I24">
         <f t="shared" si="3"/>
-        <v>2.0975000000000001</v>
+        <v>7.0975000000000001</v>
       </c>
       <c r="J24" s="6">
         <f t="shared" si="4"/>
-        <v>1.2138310185185186E-4</v>
+        <v>4.1073495370370374E-4</v>
       </c>
       <c r="K24">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="5"/>
-        <v>1.0924479166666668E-4</v>
+        <v>3.080512152777778E-4</v>
       </c>
       <c r="M24" s="8">
         <f t="shared" si="6"/>
-        <v>5.2083333333333337E-5</v>
+        <v>4.3402777777777779E-5</v>
       </c>
       <c r="N24" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="7"/>
-        <v>4.6875000000000001E-5</v>
+        <v>2.170138888888889E-5</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="8"/>
-        <v>9.8320312500000005E-5</v>
+        <v>1.540256076388889E-4</v>
+      </c>
+      <c r="R24" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S24" s="10">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U24">
+        <v>0.6</v>
+      </c>
+      <c r="V24" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="10"/>
-        <v>6.9123513844452353E-2</v>
-      </c>
-      <c r="D25" s="3">
         <f t="shared" si="12"/>
-        <v>3.4214534700003955E-3</v>
+        <v>5.1842635383339268E-2</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
       </c>
       <c r="E25" s="1">
-        <f t="shared" si="10"/>
-        <v>6.915823606667458E-2</v>
+        <f t="shared" si="12"/>
+        <v>5.2016246494450379E-2</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" si="1"/>
-        <v>3.472222222222765E-5</v>
+        <v>1.7361111111111049E-4</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="2"/>
-        <v>1.7361111111113825E-6</v>
+        <v>1.1574074074074033E-5</v>
       </c>
       <c r="H25" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I25">
         <f t="shared" si="3"/>
-        <v>1.0975000000000001</v>
+        <v>6.0975000000000001</v>
       </c>
       <c r="J25" s="6">
         <f t="shared" si="4"/>
-        <v>6.351273148148149E-5</v>
+        <v>3.5286458333333334E-4</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="5"/>
-        <v>6.351273148148149E-5</v>
+        <v>2.893489583333333E-4</v>
       </c>
       <c r="M25" s="8">
         <f t="shared" si="6"/>
-        <v>5.7870370370370373E-5</v>
+        <v>4.7453703703703694E-5</v>
       </c>
       <c r="N25" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="7"/>
-        <v>5.2083333333333337E-5</v>
+        <v>2.3726851851851847E-5</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="8"/>
-        <v>5.7161458333333347E-5</v>
+        <v>1.4467447916666665E-4</v>
+      </c>
+      <c r="R25" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S25" s="17">
+        <v>1</v>
+      </c>
+      <c r="T25" s="1">
+        <f t="shared" si="9"/>
+        <v>-5.7870370370370373E-5</v>
+      </c>
+      <c r="U25">
+        <v>0.6</v>
+      </c>
+      <c r="V25" s="1">
+        <f t="shared" si="10"/>
+        <v>-3.4722222222222222E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="10"/>
-        <v>7.2579689536674971E-2</v>
-      </c>
-      <c r="D26" s="3">
         <f t="shared" si="12"/>
-        <v>3.4214534700003955E-3</v>
+        <v>5.5298811075561886E-2</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="13"/>
+        <v>3.4561756922226175E-3</v>
       </c>
       <c r="E26" s="1">
-        <f t="shared" si="10"/>
-        <v>7.2579689536674971E-2</v>
+        <f t="shared" si="12"/>
+        <v>5.5472422186672997E-2</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.7361111111111049E-4</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0850694444444406E-5</v>
       </c>
       <c r="H26" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I26">
         <f t="shared" si="3"/>
-        <v>9.7500000000000142E-2</v>
+        <v>5.0975000000000001</v>
       </c>
       <c r="J26" s="6">
         <f t="shared" si="4"/>
-        <v>5.6423611111111193E-6</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
+        <v>2.9499421296296299E-4</v>
+      </c>
+      <c r="K26" s="7">
+        <v>0.9</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="5"/>
-        <v>5.6423611111111193E-6</v>
+        <v>2.654947916666667E-4</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="6"/>
-        <v>5.7870370370370373E-5</v>
+        <v>5.2083333333333337E-5</v>
       </c>
       <c r="N26" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" si="7"/>
-        <v>5.2083333333333337E-5</v>
+        <v>2.6041666666666668E-5</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" si="8"/>
-        <v>5.0781250000000074E-6</v>
+        <v>1.3274739583333335E-4</v>
+      </c>
+      <c r="R26" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S26" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="T26" s="1">
+        <f t="shared" si="9"/>
+        <v>-7.5231481481481487E-5</v>
+      </c>
+      <c r="U26">
+        <v>0.6</v>
+      </c>
+      <c r="V26" s="1">
+        <f t="shared" si="10"/>
+        <v>-4.5138888888888894E-5</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>21.0975</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3.4561756922226175E-3</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="10"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="12"/>
+        <v>5.8754986767784505E-2</v>
       </c>
       <c r="D27" s="3">
+        <f t="shared" ref="D27:D32" si="14">B27-TIME(0,0,3)</f>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E27" s="1">
         <f t="shared" si="12"/>
-        <v>3.4214534700003955E-3</v>
-      </c>
-      <c r="E27" s="1">
-        <f t="shared" si="10"/>
-        <v>7.2913281250000017E-2</v>
+        <v>5.8893875656673395E-2</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.3888888888888978E-4</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.1699346405229291E-6</v>
       </c>
       <c r="H27" s="1">
         <v>5.7870370370370373E-5</v>
       </c>
       <c r="I27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.0975000000000001</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3712384259259262E-4</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.1341145833333336E-4</v>
       </c>
       <c r="M27" s="8">
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.2083333333333337E-5</v>
       </c>
       <c r="N27" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O27" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.6041666666666668E-5</v>
       </c>
       <c r="P27" s="8">
         <f t="shared" si="8"/>
+        <v>1.0670572916666668E-4</v>
+      </c>
+      <c r="R27" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S27" s="10">
+        <v>2</v>
+      </c>
+      <c r="T27" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.1574074074074075E-4</v>
+      </c>
+      <c r="U27">
+        <v>0.6</v>
+      </c>
+      <c r="V27" s="1">
+        <f t="shared" si="10"/>
+        <v>-6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>18</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="12"/>
+        <v>6.2211162460007123E-2</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="12"/>
+        <v>6.2315329126673792E-2</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="1"/>
+        <v>1.0416666666666907E-4</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="2"/>
+        <v>5.7870370370371706E-6</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>3.0975000000000001</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="4"/>
+        <v>1.7925347222222225E-4</v>
+      </c>
+      <c r="K28">
+        <v>0.9</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="5"/>
+        <v>1.6132812500000004E-4</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="6"/>
+        <v>5.2083333333333343E-5</v>
+      </c>
+      <c r="N28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="7"/>
+        <v>2.6041666666666672E-5</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="8"/>
+        <v>8.066406250000002E-5</v>
+      </c>
+      <c r="R28" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S28" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="T28" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.4467592592592592E-4</v>
+      </c>
+      <c r="U28">
+        <v>0.7</v>
+      </c>
+      <c r="V28" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.0127314814814813E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>19</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="12"/>
+        <v>6.5667338152229734E-2</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="12"/>
+        <v>6.573678259667419E-2</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="1"/>
+        <v>6.94444444444553E-5</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="2"/>
+        <v>3.6549707602344896E-6</v>
+      </c>
+      <c r="H29" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>2.0975000000000001</v>
+      </c>
+      <c r="J29" s="6">
+        <f t="shared" si="4"/>
+        <v>1.2138310185185186E-4</v>
+      </c>
+      <c r="K29">
+        <v>0.9</v>
+      </c>
+      <c r="L29" s="6">
+        <f t="shared" si="5"/>
+        <v>1.0924479166666668E-4</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="6"/>
+        <v>5.2083333333333337E-5</v>
+      </c>
+      <c r="N29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O29" s="8">
+        <f t="shared" si="7"/>
+        <v>2.6041666666666668E-5</v>
+      </c>
+      <c r="P29" s="8">
+        <f t="shared" si="8"/>
+        <v>5.4622395833333342E-5</v>
+      </c>
+      <c r="R29" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S29" s="10">
+        <f t="shared" ref="S29:S31" si="15">15/5</f>
+        <v>3</v>
+      </c>
+      <c r="T29" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.7361111111111112E-4</v>
+      </c>
+      <c r="U29">
+        <v>0.8</v>
+      </c>
+      <c r="V29" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>20</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="12"/>
+        <v>6.9123513844452353E-2</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="12"/>
+        <v>6.915823606667458E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="1"/>
+        <v>3.472222222222765E-5</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
+        <v>1.7361111111113825E-6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>1.0975000000000001</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="4"/>
+        <v>6.351273148148149E-5</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="5"/>
+        <v>6.351273148148149E-5</v>
+      </c>
+      <c r="M30" s="8">
+        <f t="shared" si="6"/>
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O30" s="8">
+        <f t="shared" si="7"/>
+        <v>2.8935185185185186E-5</v>
+      </c>
+      <c r="P30" s="8">
+        <f t="shared" si="8"/>
+        <v>3.1756365740740745E-5</v>
+      </c>
+      <c r="R30" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S30" s="10">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="T30" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.7361111111111112E-4</v>
+      </c>
+      <c r="U30">
+        <v>0.9</v>
+      </c>
+      <c r="V30" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.5625E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>21</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="12"/>
+        <v>7.2579689536674971E-2</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="12"/>
+        <v>7.2579689536674971E-2</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>9.7500000000000142E-2</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="4"/>
+        <v>5.6423611111111193E-6</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="5"/>
+        <v>5.6423611111111193E-6</v>
+      </c>
+      <c r="M31" s="8">
+        <f t="shared" si="6"/>
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O31" s="8">
+        <f t="shared" si="7"/>
+        <v>2.8935185185185186E-5</v>
+      </c>
+      <c r="P31" s="8">
+        <f t="shared" si="8"/>
+        <v>2.8211805555555597E-6</v>
+      </c>
+      <c r="R31" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S31" s="10">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="T31" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.7361111111111112E-4</v>
+      </c>
+      <c r="U31">
+        <v>0.9</v>
+      </c>
+      <c r="V31" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.5625E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>21.0975</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4561756922226175E-3</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="12"/>
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4214534700003955E-3</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="12"/>
+        <v>7.2913281250000017E-2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O32" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S32" s="17">
+        <v>3</v>
+      </c>
+      <c r="T32" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.7361111111111112E-4</v>
+      </c>
+      <c r="U32">
+        <v>0.9</v>
+      </c>
+      <c r="V32" s="1">
+        <f t="shared" si="10"/>
+        <v>-1.5625E-4</v>
       </c>
     </row>
   </sheetData>
